--- a/artfynd/A 55641-2021 artfynd.xlsx
+++ b/artfynd/A 55641-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55641-2021 artfynd.xlsx
+++ b/artfynd/A 55641-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97038623</v>
+        <v>115488482</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Urgnäset, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371666.9402710097</v>
+        <v>371710</v>
       </c>
       <c r="R2" t="n">
-        <v>6928546.329177934</v>
+        <v>6928430</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97039514</v>
+        <v>110593912</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,44 +783,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Urgnäset 115, Härjedalen, Hjd</t>
+          <t>V om Urgnäset, Funäsdalen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>371613.9699638943</v>
+        <v>371520</v>
       </c>
       <c r="R3" t="n">
-        <v>6928471.498137605</v>
+        <v>6928648</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,33 +854,54 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Betula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110593912</v>
+        <v>110593864</v>
       </c>
       <c r="B4" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>371519.6927297312</v>
+        <v>371649</v>
       </c>
       <c r="R4" t="n">
-        <v>6928648.327785504</v>
+        <v>6928550</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -989,19 +969,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,31 +983,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Betula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1054,56 +999,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110593864</v>
+        <v>115488689</v>
       </c>
       <c r="B5" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V om Urgnäset, Funäsdalen, Hjd</t>
+          <t>Urgnäset 115, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>371648.9877346572</v>
+        <v>371642</v>
       </c>
       <c r="R5" t="n">
-        <v>6928549.799628571</v>
+        <v>6928416</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,22 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,34 +1078,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115489092</v>
+        <v>97038266</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,24 +1125,26 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyren (Långmyren), Hjd</t>
+          <t>Urgnäset, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>371465</v>
+        <v>371710</v>
       </c>
       <c r="R6" t="n">
-        <v>6928574</v>
+        <v>6928430</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,22 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,27 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115488689</v>
+        <v>97038448</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,37 +1211,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Urgnäset 115, Hjd</t>
+          <t>Urgnäset, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>371642</v>
+        <v>371713</v>
       </c>
       <c r="R7" t="n">
-        <v>6928416</v>
+        <v>6928440</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,12 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,15 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115489110</v>
+        <v>97038623</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,23 +1337,22 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyren, Hjd</t>
+          <t>Urgnäset, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>371380</v>
+        <v>371667</v>
       </c>
       <c r="R8" t="n">
-        <v>6928613</v>
+        <v>6928546</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,12 +1376,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,6 +1405,545 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97039514</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Urgnäset 115, Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>371614</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6928471</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-11-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-11-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115489092</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmyren, Långmyren, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>371465</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6928574</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Bengtson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Bengtson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115489110</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmyren, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>371380</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6928613</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110234283</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långmyren, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>371553</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6928561</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115841326</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Urgnäset, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>371698</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6928415</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55641-2021 artfynd.xlsx
+++ b/artfynd/A 55641-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115488482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110593912</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110593864</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115488689</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97038266</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97038448</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97038623</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97039514</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115489092</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115489110</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234283</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,8 +2004,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115841326</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>